--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.91925</v>
+        <v>16.75937</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52305</v>
+        <v>16.66865</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76699</v>
+        <v>16.67105</v>
       </c>
       <c r="F2" t="n">
-        <v>42.32865</v>
+        <v>42.02266</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05023</v>
+        <v>0.05087</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81939</v>
+        <v>1.80386</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.00437</v>
+        <v>17.00507</v>
       </c>
       <c r="D3" t="n">
-        <v>16.52754</v>
+        <v>16.73088</v>
       </c>
       <c r="E3" t="n">
-        <v>16.63168</v>
+        <v>16.81914</v>
       </c>
       <c r="F3" t="n">
-        <v>41.72679</v>
+        <v>43.42374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05152</v>
+        <v>0.05019</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81609</v>
+        <v>1.78963</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.15308</v>
+        <v>16.82333</v>
       </c>
       <c r="D4" t="n">
-        <v>16.75563</v>
+        <v>16.39053</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63992</v>
+        <v>16.67187</v>
       </c>
       <c r="F4" t="n">
-        <v>42.33468</v>
+        <v>43.12171</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05198</v>
+        <v>0.04992</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83791</v>
+        <v>1.84904</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.4205</v>
+        <v>16.51033</v>
       </c>
       <c r="D6" t="n">
-        <v>15.92234</v>
+        <v>15.87568</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75457</v>
+        <v>16.49633</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4703</v>
+        <v>21.8544</v>
       </c>
       <c r="G6" t="n">
-        <v>34.09833</v>
+        <v>35.66787</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.73102</v>
+        <v>16.7611</v>
       </c>
       <c r="D7" t="n">
-        <v>16.15921</v>
+        <v>15.97741</v>
       </c>
       <c r="E7" t="n">
-        <v>16.28865</v>
+        <v>16.40273</v>
       </c>
       <c r="F7" t="n">
-        <v>21.62098</v>
+        <v>21.53025</v>
       </c>
       <c r="G7" t="n">
-        <v>34.33747</v>
+        <v>34.4643</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.53995</v>
+        <v>17.21231</v>
       </c>
       <c r="D8" t="n">
-        <v>15.90225</v>
+        <v>15.94669</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3163</v>
+        <v>16.68588</v>
       </c>
       <c r="F8" t="n">
-        <v>21.78263</v>
+        <v>21.40889</v>
       </c>
       <c r="G8" t="n">
-        <v>33.30667</v>
+        <v>34.34275</v>
       </c>
     </row>
   </sheetData>
